--- a/docs/dareomotosho-services.xlsx
+++ b/docs/dareomotosho-services.xlsx
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>422 'invalid from' = sender not on the verified domain or malformed env var (now sanitized by lib/email.ts safeSender).</t>
+          <t>Rate limit: 5 requests / 10 min per IP. 422 'invalid from' = sender not on the verified domain or malformed env var (now sanitized by lib/email.ts safeSender).</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>GET reports key presence, audience list, and the ID in use. 409 (already subscribed) counts as success.</t>
+          <t>Rate limit: 8 requests / 10 min per IP (POST). GET reports key presence, audience list, and the ID in use. 409 (already subscribed) counts as success.</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Reply-To set as a raw header to avoid the reply_to/replyTo API naming variance. Honeypot hits return fake success.</t>
+          <t>Rate limits: POST 5 / 10 min per IP; ?send=test 2 / 10 min. Reply-To set as a raw header to avoid the reply_to/replyTo naming variance. Honeypot hits return fake success. All /api/* responses carry X-Robots-Tag: noindex.</t>
         </is>
       </c>
     </row>

--- a/docs/dareomotosho-services.xlsx
+++ b/docs/dareomotosho-services.xlsx
@@ -651,7 +651,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Google Calendar appointment schedule</t>
+          <t>Calendly</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The /book page links to a Google Calendar appointment-scheduling page for mentorship/advisory calls</t>
+          <t>The /book page links to a Calendly scheduling page (35-minute calls) for mentorship/advisory</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Free tier</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>bookingUrl in lib/site.ts</t>
+          <t>bookingUrl in lib/site.ts (calendly.com/darelekan46/35min)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>calendar.google.com</t>
+          <t>calendly.com dashboard</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Active. Data entered on Google's page is processed by Google (listed in the privacy policy).</t>
+          <t>Active since July 2026, replacing the earlier Google Calendar appointment page. Data entered on Calendly's page is processed by Calendly (listed in the privacy policy).</t>
         </is>
       </c>
     </row>

--- a/docs/dareomotosho-services.xlsx
+++ b/docs/dareomotosho-services.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The /book page links to a Calendly scheduling page (35-minute calls) for mentorship/advisory</t>
+          <t>The /book page links to a Calendly scheduling page (30-minute calls) for mentorship/advisory</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">

--- a/docs/dareomotosho-services.xlsx
+++ b/docs/dareomotosho-services.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>API routes: /api/email-result, /api/contact, /api/subscribe</t>
+          <t>API routes: /api/email-result, /api/contact, /api/subscribe, /api/resources/welcome</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/api/subscribe</t>
+          <t>/api/subscribe (Subscribe form + Field Kit gate)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/api/email-result</t>
+          <t>/api/email-result, /api/resources/welcome</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Overrides the Path Finder results sender</t>
+          <t>Overrides the results / Field Kit sender address</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Default: Dare Omotosho &lt;results@email.dareomotosho.com&gt;. Must be on the Resend-verified domain. Values are sanitized (quotes/whitespace repaired).</t>
+          <t>Default: Dare Omotosho &lt;results@email.dareomotosho.com&gt;. Must be on a domain verified in Resend — the root domain is not verified, email.dareomotosho.com is. Quotes and angle brackets are sanitised by lib/email.ts safeSender(), because a mangled paste here returns a 422 from Resend.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>POST adds a contact to the Resend audience (Supabase kept as backup list by the client). GET is a config diagnostic</t>
+          <t>POST adds a contact to the Resend audience (the one email list, shared by the Subscribe form and the Field Kit gate). GET is a no-secrets diagnostic that reports whether audience access works.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Rate limit: 8 requests / 10 min per IP (POST). GET reports key presence, audience list, and the ID in use. 409 (already subscribed) counts as success.</t>
+          <t>Rate limit: 8 requests / 10 min per IP. Audience is auto-discovered; RESEND_AUDIENCE_ID pins one, and a wrong value falls back to discovery. A contact conflict (409) is success and is reported back as alreadySubscribed:true so the UI can say so and skip the welcome email. A sending-only API key fails audience writes — GET says so in plain words.</t>
         </is>
       </c>
     </row>
@@ -1439,6 +1439,87 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Track OG image revalidates every 24 h so LinkedIn's crawler gets a cached, instant response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>/api/resources/[slug]</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Node.js</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Returns the gated remainder of a Field Kit sheet as markdown, so the gated half never ships inside the crawlable page HTML.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>401 without the resources_unlocked cookie. The gate is a courtesy, not an authorisation boundary — the kits are free and nothing private sits behind it, so a hand-set cookie is an accepted outcome, not a vulnerability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>/api/resources/[slug]/download</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Node.js</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>The kit as a printable A4 PDF, rendered from the same markdown by lib/resource-pdf.tsx so fill-in tables survive as tables with room to write.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>401 without the resources_unlocked cookie. Must stay on the Node runtime: @react-pdf/renderer does not run on Edge. Verify changes by extracting the PDF's text, not by trusting HTTP 200 — a footer that renders nothing still returns 200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>/api/resources/welcome</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Node.js</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>One confirmation email after a reader's first Field Kit unlock, naming the kit and linking back to it and to the shelf.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Two caps: 5 requests / 10 min per IP, and one send per email address per 24h. The per-address cap is claimed before the send and released if the send fails, so a transient Resend error does not cost the reader their email for a day. The limiter is in-memory, so on serverless it holds per warm instance — the client-side skip is the first line of defence, this is the backstop. Never blocks the unlock.</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1771,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>^10.4.20 / ^8.5.1</t>
+          <t>^10.4.20 / ^8.5.23</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1700,7 +1781,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>CSS pipeline</t>
+          <t>CSS pipeline. The postcss floor was raised in Aug 2026 so a fresh install cannot resolve a version affected by GHSA-qx2v-qp2m-jg93 and the sourceMappingURL advisories. Note that next pins its own nested postcss 8.4.31, which only a Next.js 16 upgrade moves.</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1815,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>^0.5.18</t>
+          <t>^0.6.0</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1744,7 +1825,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Used by one-off content tooling (docx extraction during content import)</t>
+          <t>Used by one-off content tooling (.odt reading in scripts/seed.js). Floor raised from ^0.5.18 in Aug 2026: GHSA-xcpc-8h2w-3j85, a crafted ZIP triggering a 4GB allocation.</t>
         </is>
       </c>
     </row>
